--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20232.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -80,6 +80,33 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>LEONARDO GABRIEL</t>
+  </si>
+  <si>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
   </si>
 </sst>
 </file>
@@ -623,16 +650,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>77.42</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -646,16 +676,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>68.56999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -669,16 +702,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,16 +728,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -757,16 +796,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>80.65000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -783,16 +822,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>82.86</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -809,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>91.43000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -844,7 +883,7 @@
         <v>91.67</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -854,7 +893,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -884,6 +923,75 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920166</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920367</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920282</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20232.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>MOLINA</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>OLMEDO</t>
   </si>
   <si>
@@ -94,6 +97,9 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -101,6 +107,9 @@
   </si>
   <si>
     <t>LEONARDO GABRIEL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>SERGIO FARITH</t>
@@ -893,7 +902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -931,10 +940,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -948,22 +957,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920367</v>
+        <v>23330051920062</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -971,16 +980,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920282</v>
+        <v>22330051920367</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -989,6 +998,29 @@
         <v>13</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920282</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20232.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,42 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>LEONARDO GABRIEL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
   </si>
 </sst>
 </file>
@@ -805,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>77.42</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -831,16 +795,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>68.56999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -857,16 +821,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -883,13 +847,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
         <v>8</v>
@@ -902,7 +866,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -932,98 +896,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920166</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920062</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920367</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920282</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
